--- a/astro-site/public/dl/kit-tareas-dark-kitchen/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/01-apertura-cierre.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre Cocina" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Cocina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Cocina" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura Cocina'!$A$1:$G$40</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Cierre Cocina'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre Cocina'!$A$1:$G$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -136,44 +141,60 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -533,15 +554,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -549,6 +571,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -556,6 +579,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -570,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -577,8 +602,33 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -592,16 +642,16 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist de Apertura — Cocina de Producción</t>
@@ -615,10 +665,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -643,7 +694,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -660,10 +711,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -689,10 +738,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -718,10 +765,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -747,10 +792,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -776,10 +819,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -812,10 +853,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -841,10 +880,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -870,10 +907,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -899,10 +934,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -928,10 +961,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -957,10 +988,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -993,10 +1022,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1022,10 +1049,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1051,10 +1076,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1080,10 +1103,8 @@
       <c r="G21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="18" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
@@ -1109,10 +1130,8 @@
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="19" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1145,10 +1164,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="19" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -1174,10 +1191,8 @@
       <c r="G25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="18" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
@@ -1203,10 +1218,8 @@
       <c r="G26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="19" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -1232,10 +1245,8 @@
       <c r="G27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="18" t="n">
+        <v>20</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
@@ -1261,10 +1272,8 @@
       <c r="G28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="19" t="n">
+        <v>21</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
@@ -1290,10 +1299,8 @@
       <c r="G29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="18" t="n">
+        <v>22</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -1326,10 +1333,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="18" t="n">
+        <v>23</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -1355,10 +1360,8 @@
       <c r="G32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="19" t="n">
+        <v>24</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
@@ -1384,10 +1387,8 @@
       <c r="G33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A34" s="18" t="n">
+        <v>25</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
@@ -1412,6 +1413,7 @@
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="C36" s="15" t="inlineStr">
         <is>
@@ -1420,14 +1422,19 @@
       </c>
       <c r="D36" s="16">
         <f>COUNTIF(F5:F34,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>de 25</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F36">
+        <f>COUNTIF(B5:B34,"?*")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -1435,6 +1442,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
@@ -1454,7 +1462,17 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G34">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F25 F26 F27 F28 F29 F30 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1469,16 +1487,16 @@
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Checklist de Cierre — Cocina de Producción</t>
@@ -1492,10 +1510,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1520,7 +1539,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1537,10 +1556,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1566,10 +1583,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1595,10 +1610,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1624,10 +1637,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1660,10 +1671,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -1689,10 +1698,8 @@
       <c r="G11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1718,10 +1725,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1747,10 +1752,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1776,10 +1779,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1812,10 +1813,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1841,10 +1840,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1870,10 +1867,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1899,10 +1894,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1928,10 +1921,8 @@
       <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="19" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -1964,10 +1955,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="19" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
@@ -1993,10 +1982,8 @@
       <c r="G23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="18" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
@@ -2022,10 +2009,8 @@
       <c r="G24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="19" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
@@ -2051,10 +2036,8 @@
       <c r="G25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="18" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
@@ -2080,10 +2063,8 @@
       <c r="G26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="19" t="n">
+        <v>19</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -2116,10 +2097,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="19" t="n">
+        <v>20</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
@@ -2145,10 +2124,8 @@
       <c r="G29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="18" t="n">
+        <v>21</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
@@ -2174,10 +2151,8 @@
       <c r="G30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
@@ -2203,10 +2178,8 @@
       <c r="G31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="18" t="n">
+        <v>23</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
@@ -2231,6 +2204,7 @@
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="C34" s="15" t="inlineStr">
         <is>
@@ -2239,14 +2213,19 @@
       </c>
       <c r="D34" s="16">
         <f>COUNTIF(F5:F32,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>de 23</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F34">
+        <f>COUNTIF(B5:B32,"?*")</f>
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -2254,6 +2233,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
@@ -2269,11 +2249,21 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G32">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21 F23 F24 F25 F26 F27 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/01-apertura-cierre.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Cocina" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre Cocina'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre Cocina'!$A$1:$G$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -637,7 +639,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1472,8 +1474,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1482,7 +1492,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2249,9 +2259,9 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2263,7 +2273,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/01-apertura-cierre.xlsx
@@ -12,10 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Cocina" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura Cocina'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre Cocina'!$A$1:$G$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre Cocina'!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +87,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +133,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -145,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +201,49 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,65 +621,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Tareas de Apertura y Cierre — Dark Kitchen</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists diarios para abrir y cerrar tu dark kitchen / ghost kitchen.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Una dark kitchen no tiene sala ni terraza — todo es producción y delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• El foco está en tablets, packaging, tiempos de entrega y riders</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>▸ Estás en 01-apertura-cierre.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -641,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -706,771 +870,1024 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGIENE PERSONAL</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Uniforme y calzado de trabajo limpios, delantal cambiado y pelo recogido (gorro o redecilla)</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Sin anillos, reloj ni pulseras; uñas cortas, limpias y sin esmalte</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Heridas y cortes cubiertos con apósito impermeable de color visible y guante encima</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Lavado de manos al entrar y en cada cambio de tarea o de marca; lavamanos con jabón, papel y agua caliente</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Todo el equipo</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Declarar síntomas digestivos o respiratorios: quien los tenga no manipula alimentos</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Encargado/a</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPOS</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Encender todos los equipos: plancha, horno, freidora, fogones</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Encender la campana extractora y ventilar la cocina ANTES de encender nada más</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Encender campana extractora</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Verificar el gas ANTES de encender nada: abrir la llave general y comprobar que NO huele a gas; si huele, no enciendas, ventila y avisa al mantenedor</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Verificar temperaturas de cámaras frigoríficas</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Encender los equipos en este orden: plancha, horno, freidora y fogones</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Encender baño maría si aplica</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Verificar gas: llaves abiertas, sin fugas</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Comprobar que las cámaras frigoríficas han funcionado toda la noche y registrar temperatura (refrigeración 0-4 °C) — anota la lectura: ____ °C. Si hay desviación, no uses el género hasta valorarlo</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  MISE EN PLACE</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Preparar mise en place de todas las marcas/conceptos</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Preparar salsas del día (caseras)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Cortar vegetales, proteínas, guarniciones</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Pre-cocinar bases: arroces, pasta, fondos</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Montar estaciones de producción por marca</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de cada ingrediente en línea</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PACKAGING Y DELIVERY</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de envases por marca (cajas, bowls, bolsas)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Verificar stock de cubiertos desechables, servilletas, salsas</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de bolsas de delivery con logo</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Verificar precintos de seguridad / stickers</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Montar estación de empaquetado: envases, bolsas, ticket</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  TABLETS Y PLATAFORMAS</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Encender todas las tablets de delivery</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Verificar conexión wifi / datos en cada tablet</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Activar todas las marcas en Glovo, Uber Eats, Just Eat</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Verificar que menús están actualizados (precios, disponibilidad)</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>Verificar que la información de ALÉRGENOS de cada plato sigue publicada y actualizada en la ficha de cada marca: en venta a distancia es obligatorio darla antes de que el cliente compre</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>Encargado/a</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Verificar impresora de tickets funcionando</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="28" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Pausar marcas si no hay stock de algo (86)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HIGIENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Lavarse manos, uniforme completo</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGIENE DE SUPERFICIES Y BOTIQUÍN</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="24" t="n"/>
+      <c r="G38" s="24" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Comprobar que el botiquín y el extintor están accesibles y sin cajas de packaging delante</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>Desinfectar superficies de trabajo</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="28" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="n">
+        <v>31</v>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Verificar jabón y papel en dispensadores</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>Cocinero apertura</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D36" s="16">
-        <f>COUNTIF(F5:F34,"✓")</f>
+      <c r="F41" s="28" t="n"/>
+      <c r="G41" s="28" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="n"/>
+      <c r="B42" s="32" t="n"/>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="28" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="28" t="n"/>
+      <c r="G43" s="28" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="n"/>
+      <c r="B44" s="32" t="n"/>
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="28" t="n"/>
+      <c r="G44" s="28" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n"/>
+      <c r="B45" s="32" t="n"/>
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="28" t="n"/>
+      <c r="G45" s="28" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="n"/>
+      <c r="B46" s="32" t="n"/>
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="27" t="n"/>
+      <c r="E46" s="27" t="n"/>
+      <c r="F46" s="28" t="n"/>
+      <c r="G46" s="28" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D48" s="16">
+        <f>COUNTIFS(B5:B46,"?*",F5:F46,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F36">
-        <f>COUNTIF(B5:B34,"?*")</f>
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="F48">
+        <f>COUNTIF(B5:B46,"?*")-COUNTIF(F5:F46,"N/A")</f>
+        <v>31.0</v>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="11">
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G34">
+  <conditionalFormatting sqref="A5:G46">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F25 F26 F27 F28 F29 F30 F32 F33 F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F22 F23 F25 F26 F27 F28 F29 F31 F32 F33 F34 F35 F36 F37 F39 F40 F41 F42 F43 F44 F45 F46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1494,7 +1911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1559,717 +1976,821 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRODUCTO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Etiquetar y fechar todas las pre-elaboraciones</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Guardar salsas en recipientes herméticos</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Cubrir y refrigerar toda la mise en place</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Congelar lo que no se usará mañana</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Congelar EN EL DÍA lo que no se usará mañana, en porciones de un solo uso y etiquetado con la fecha (vida útil por familia en la tabla del pie de «FIFO Semanal», en 05-tareas-semanales-mensuales.xlsx)</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Anotar las mermas del día por marca (producto, cantidad y motivo): sin ese dato el food cost por marca del mes sale mal</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Cocinero cierre</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPOS</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Apagar plancha, horno, freidora, fogones</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Filtrar o cambiar aceite de freidora si toca</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Filtrar o cambiar el aceite de la freidora si toca: manipularlo SÓLO por debajo de 40 °C, nunca en caliente, con guantes y recipiente estable; el usado, al bidón del gestor autorizado</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Apagar campana extractora</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Verificar cámaras cerradas y a temperatura</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Verificar cámaras cerradas y a temperatura (refrigeración 0-4 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Cerrar llave de gas</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  LIMPIEZA</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Limpiar todas las superficies y estaciones</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Fregar utensilios, bandejas, cacerolas</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Barrer y fregar suelo</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Sacar basura y reciclar (mucho cartón en dark kitchen)</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Limpiar estación de empaquetado</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  TABLETS Y CIERRE</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Desactivar todas las marcas en plataformas</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Apagar tablets de delivery</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Cuadrar pedidos del día vs facturación plataformas</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Anotar incidencias: pedidos cancelados, reembolsos, quejas</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>22:15</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Hacer pedidos para mañana</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN MAÑANA</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Descongelar lo necesario para mañana</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Anotar faltantes por marca</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="n">
-        <v>22</v>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="F31" s="28" t="n"/>
+      <c r="G31" s="28" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Preparar lista de mise en place del día siguiente</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>Cocinero cierre</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Apagar luces y activar alarma</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Encargado/a</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-    </row>
-    <row r="33"/>
+      <c r="F33" s="28" t="n"/>
+      <c r="G33" s="28" t="n"/>
+    </row>
     <row r="34">
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D34" s="16">
-        <f>COUNTIF(F5:F32,"✓")</f>
+      <c r="A34" s="31" t="n"/>
+      <c r="B34" s="32" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="28" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n"/>
+      <c r="B35" s="32" t="n"/>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="28" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="n"/>
+      <c r="B36" s="32" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="28" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="n"/>
+      <c r="B38" s="32" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D40" s="16">
+        <f>COUNTIFS(B5:B38,"?*",F5:F38,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F34">
-        <f>COUNTIF(B5:B32,"?*")</f>
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="F40">
+        <f>COUNTIF(B5:B38,"?*")-COUNTIF(F5:F38,"N/A")</f>
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Dark Kitchen · AI Chef Pro · aichef.pro —</t>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A36:G36"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G32">
+  <conditionalFormatting sqref="A5:G38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F17 F18 F19 F20 F21 F23 F24 F25 F26 F27 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F22 F24 F25 F26 F27 F28 F30 F31 F32 F33 F34 F35 F36 F37 F38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
